--- a/02_screening/screening.xlsx
+++ b/02_screening/screening.xlsx
@@ -1,13 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Screening" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FullText_Screening" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normative_sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,21 +29,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,10 +51,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,22 +424,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="16.2" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15.3" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12.6" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,27 +463,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>source_database</t>
+          <t>identified_via</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>title_abstract_decision</t>
+          <t>ta_decision</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>title_abstract_reason_code</t>
+          <t>ft_decision</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>full_text_decision</t>
+          <t>ft_reason_code</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>full_text_reason_code</t>
+          <t>ft_reason</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -497,184 +493,941 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>screening_date</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>study_id_if_included</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EXAMPLE_Smith2022_CloudGovernanceSurvey</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EXAMPLE: A Survey of Governance Models for Multi-Cloud Environments</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Smith, J.; Doe, A.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EBSCOhost</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TEMPLATE Reviewer</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>STU-0001</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - replace with real screening decision</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Data security and governance in multi-cloud computing environment</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EXAMPLE_Lee2021_PolicyOrchestration</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EXAMPLE: Policy Orchestration Across Heterogeneous Cloud Providers</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Lee, K.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Cloud security frameworks: A comparison to evaluate cloud control standards</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Security issues in multi-cloud: A systematic literature review</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>On the comparative analysis of trends in cybersecurity risk assessment, governance, and compliance frameworks</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Privacy-preserving identity and access management in multiple cloud environments: Models, issues, and solutions</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Multi-cloud security model: Establishment of inter-server communication for authentication integrity</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>A systematic literature review on cloud computing security: Threats and mitigation strategies</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Security and privacy in multi-cloud and hybrid cloud environments</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Information security governance challenges and critical success factors: Systematic review</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>citation tracking</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Reference service model for federated identity management</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EBSCOhost</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TEMPLATE Reviewer</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>STU-0002</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - replace with real screening decision</t>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>citation tracking</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EXCL-Reece2023</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Systemic Risk and Vulnerability Analysis of Multi-cloud Environments</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Reece et al.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>citation tracking</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>FT-NPR</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Not peer-reviewed</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>EXCL-Tabrizchi2020</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>A survey on security challenges in cloud computing: issues, threats, and solutions</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Tabrizchi &amp; Kuchaki Rafsanjani</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>FT-SCOPE</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Single-cloud focus only - no multi-cloud governance framework analysis</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>EXCL-Li2021</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Blockchain-based trust management in cloud computing systems: a taxonomy, review and future directions</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Li et al.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>FT-SCOPE</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Blockchain trust management focus - no cybersecurity governance framework analysis</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>EXCL-Brumă2023</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Incident Response: a Comprehensive Analysis</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Brumă</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>FT-SCOPE</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Incident response focus -  outside governance framework scope</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EXCL-Chaudhari2023</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>A review on cloud security issues and solutions</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Chaudhari et al.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>FT-SCOPE</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>General cloud security survey - no governance framework or multi-cloud analysis</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EXCL-Abioye2021</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Cloud-Based Business Process Security Risk Management: a systematic review</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Abioye et al.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>database search</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>FT-SCOPE</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Business process risk management focus - not a multi-cloud governance framework comparison</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="29.7" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 primary normative source added directly; outside PRISMA screening; exempt from quality assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 primary normative source added directly; outside PRISMA screening; exempt from quality assessment.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TEMPLATE_Nguyen2020_ComplianceFramework</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TEMPLATE: A Compliance Framework for Cross-Cloud Data Governance</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nguyen, T.; Fischer, R.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>EBSCOhost</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Exclude</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TEMPLATE Reviewer</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>TEMPLATE row - excluded at title/abstract stage, single-cloud only</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 primary normative source added directly; outside PRISMA screening; exempt from quality assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 primary normative source added directly; outside PRISMA screening; exempt from quality assessment.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Record-level title/abstract decisions for the 1,599 deduplicated records were not archived; only aggregate counts exist (1,583 excluded for topical irrelevance, publication type, scope, language). See docs/known_issues.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Full-text decisions: single reviewer (SS). ETECOM 2026 Fig. 1: 5 excluded as outside multi-cloud governance scope, 1 as not peer-reviewed (identified via citation tracking).</t>
         </is>
       </c>
     </row>
